--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2021_T4_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2021_T4_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>67</t>
+    <t>61</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>2.657</t>
-  </si>
-  <si>
-    <t>(0.625)</t>
-  </si>
-  <si>
-    <t>8.881</t>
-  </si>
-  <si>
-    <t>(1.019)</t>
-  </si>
-  <si>
-    <t>8.800</t>
-  </si>
-  <si>
-    <t>(5.391)</t>
-  </si>
-  <si>
-    <t>22.303</t>
-  </si>
-  <si>
-    <t>(10.619)</t>
-  </si>
-  <si>
-    <t>6.641</t>
-  </si>
-  <si>
-    <t>(5.314)</t>
-  </si>
-  <si>
-    <t>9.000</t>
-  </si>
-  <si>
-    <t>(1.130)</t>
-  </si>
-  <si>
-    <t>3.711</t>
-  </si>
-  <si>
-    <t>(0.654)</t>
-  </si>
-  <si>
-    <t>0.495</t>
-  </si>
-  <si>
-    <t>(0.125)</t>
-  </si>
-  <si>
-    <t>36.206</t>
-  </si>
-  <si>
-    <t>(22.821)</t>
-  </si>
-  <si>
-    <t>10.646</t>
-  </si>
-  <si>
-    <t>(2.381)</t>
+    <t>1.813</t>
+  </si>
+  <si>
+    <t>(0.381)</t>
+  </si>
+  <si>
+    <t>9.623</t>
+  </si>
+  <si>
+    <t>(1.073)</t>
+  </si>
+  <si>
+    <t>2.658</t>
+  </si>
+  <si>
+    <t>(0.454)</t>
+  </si>
+  <si>
+    <t>9.064</t>
+  </si>
+  <si>
+    <t>(1.039)</t>
+  </si>
+  <si>
+    <t>1.422</t>
+  </si>
+  <si>
+    <t>(0.215)</t>
+  </si>
+  <si>
+    <t>9.836</t>
+  </si>
+  <si>
+    <t>(1.188)</t>
+  </si>
+  <si>
+    <t>2.644</t>
+  </si>
+  <si>
+    <t>(0.436)</t>
+  </si>
+  <si>
+    <t>0.527</t>
+  </si>
+  <si>
+    <t>(0.136)</t>
+  </si>
+  <si>
+    <t>11.418</t>
+  </si>
+  <si>
+    <t>(1.451)</t>
+  </si>
+  <si>
+    <t>6.841</t>
+  </si>
+  <si>
+    <t>(0.822)</t>
   </si>
   <si>
     <t>49</t>
@@ -198,7 +198,7 @@
     <t>(1.780)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-0.753</t>
-  </si>
-  <si>
-    <t>2.875</t>
-  </si>
-  <si>
-    <t>-2.488</t>
-  </si>
-  <si>
-    <t>-8.556</t>
-  </si>
-  <si>
-    <t>-5.084</t>
-  </si>
-  <si>
-    <t>1.510</t>
-  </si>
-  <si>
-    <t>-0.208</t>
-  </si>
-  <si>
-    <t>-0.023</t>
-  </si>
-  <si>
-    <t>-18.583</t>
-  </si>
-  <si>
-    <t>-0.138</t>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>2.132</t>
+  </si>
+  <si>
+    <t>3.654***</t>
+  </si>
+  <si>
+    <t>4.683**</t>
+  </si>
+  <si>
+    <t>0.134</t>
+  </si>
+  <si>
+    <t>0.674</t>
+  </si>
+  <si>
+    <t>0.859</t>
+  </si>
+  <si>
+    <t>-0.055</t>
+  </si>
+  <si>
+    <t>6.205**</t>
+  </si>
+  <si>
+    <t>3.667**</t>
   </si>
 </sst>
 </file>
